--- a/config/excel/monsters.xlsx
+++ b/config/excel/monsters.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="monsters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,30 +423,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,102 +465,142 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>spawn_order</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>unlock_at_stage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>name_cn</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>def</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>attack_interval</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>color_hex</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>grade</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>can_move</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>attack_range</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arrow_speed</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ranged</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ki_drain_on_hit</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>max_split_tier</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>split_count</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>exp_reward</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>character_folder</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>sprite_prefix</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>projectile_folder</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>attack_pattern</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>projectile_effect</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>spread_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>spread_angle_deg</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>bounce_count</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sprite_tint_hex</t>
         </is>
       </c>
     </row>
@@ -562,47 +610,47 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>普通怪</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>80</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1.15</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>13</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>19</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>#526078</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -617,142 +665,182 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>Skeleton</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Skeleton</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELITE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>高级怪</t>
-        </is>
+          <t>ARCHER</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>110</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>射箭怪</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="F3" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>21</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>#8a6aa8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
+        <v>1.35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>#6a8a5a</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Elite Orc</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Elite Orc</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arrow(projectile)</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SHIELD</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>盾牌怪</t>
-        </is>
+          <t>ELITE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>120</v>
-      </c>
-      <c r="D4" t="n">
         <v>5</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>高级怪</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="F4" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>#5f7a88</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+        <v>1.05</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>#8a6aa8</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -767,325 +855,726 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Knight</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Knight</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Elite Orc</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Elite Orc</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BERSERKER</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>狂战士</t>
-        </is>
+          <t>FIRE_MAGE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>火焰法师</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>90</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.85</v>
-      </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>#b85a4a</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>C/B</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
+        <v>2.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>#501818</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Armored Axeman</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Armored Axeman</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Magic(projectile)</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPLITTER</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>分裂怪</t>
-        </is>
+          <t>SHIELD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>70</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>盾牌怪</t>
+        </is>
       </c>
       <c r="E6" t="n">
+        <v>150</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>#5f7a88</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>8</v>
       </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>18</v>
-      </c>
-      <c r="H6" t="n">
-        <v>14</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>#7b9f5a</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>A+/C/C</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Slime</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Slime</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARCHER</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>射箭怪</t>
-        </is>
+          <t>CROSS_SHOOTER</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>75</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>十字子弹怪</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>#6a8a5a</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>215</v>
+        <v>1.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>#8a7898</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>S/A/B/A</t>
+        </is>
       </c>
       <c r="M7" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Archer</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Archer</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Arrow(projectile)</t>
-        </is>
-      </c>
+          <t>Priest</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Priest</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Magic(projectile)</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>enemy_cross_magic</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FIRE_MAGE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>火焰法师</t>
-        </is>
+          <t>BERSERKER</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
       </c>
       <c r="C8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>狂战士</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>#b85a4a</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>C/B</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Armored Axeman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Armored Axeman</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SHOTGUN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>霰弹怪</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>80</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>#6a7078</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>S/A/B/A</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>215</v>
+      </c>
+      <c r="O9" t="n">
+        <v>85</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skeleton Archer</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skeleton Archer</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arrow(projectile)</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>enemy_shotgun_arrow</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SPLITTER</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>分裂怪</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>70</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>18</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>#7b9f5a</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>A+/C/C</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BOUNCE_SLIME</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>反弹子弹怪</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>80</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
         <v>12</v>
       </c>
-      <c r="H8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>#501818</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>250</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="H11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>#b84040</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>S/A/B/A</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>70</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Wizard</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Wizard</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Magic(projectile)</t>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>bounce</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>enemy_bounce_blob</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>#ff6868</t>
         </is>
       </c>
     </row>
